--- a/dba-script-generator/samples/TEMPLATE.xlsx
+++ b/dba-script-generator/samples/TEMPLATE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Meta" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Columns" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Operations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MyInserts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MyData" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;Col1&gt;</t>
+          <t>KeyCol</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -600,17 +600,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>&lt;Col2&gt;</t>
+          <t>DataCol</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>nvarchar(36)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PARAM:EffectiveDate</t>
+          <t>CELL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -618,17 +618,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&lt;Col3&gt;</t>
+          <t>EffDate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>char(1)</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CONST:Y</t>
+          <t>PARAM:EffectiveDate</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -636,20 +636,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>&lt;Col4&gt;</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>char(1)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CONST:Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DecodeCol</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>nvarchar(36)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ECHO:&lt;Col1&gt;</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ECHO:DataCol</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -718,14 +736,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MyInserts</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Insert</t>
-        </is>
-      </c>
+          <t>MyData</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>INSERT (or UPDATE / DELETE)</t>
@@ -733,7 +747,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt;comma,separated,key,columns&gt;</t>
+          <t>KeyCol  (columns that uniquely identify a record)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -768,40 +782,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>KeyCol</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>&lt;Col1&gt;</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>&lt;Col2&gt;</t>
+          <t>DataCol</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Insert</t>
+          <t>&lt;key value&gt;</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>&lt;value&gt;</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>&lt;value&gt;</t>
+          <t>&lt;data value&gt;</t>
         </is>
       </c>
     </row>
